--- a/students/ندرلوhip5.2ok.xlsx
+++ b/students/ندرلوhip5.2ok.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B953DAD8-48EE-4566-99D4-EA9466D17677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -93,12 +94,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -111,7 +112,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -134,25 +135,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -426,22 +444,22 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
-    <col min="7" max="7" width="40.42578125" customWidth="1"/>
+    <col min="4" max="4" width="9.09765625" customWidth="1"/>
+    <col min="5" max="5" width="13.59765625" customWidth="1"/>
+    <col min="6" max="6" width="13.3984375" customWidth="1"/>
+    <col min="7" max="7" width="40.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -480,88 +498,88 @@
       <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>33544792</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="3">
         <v>9196990305</v>
       </c>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>111234</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="2">
         <v>9127434798</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="2"/>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>111157</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="2">
         <v>9199805574</v>
       </c>
-      <c r="F4" s="5"/>
+      <c r="F4" s="3"/>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>11156</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="2">
         <v>9122415741</v>
       </c>
-      <c r="F5" s="5"/>
+      <c r="F5" s="3"/>
       <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>11185</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="2">
         <v>9104760579</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>33526445</v>
       </c>
       <c r="G6" s="1">
@@ -569,22 +587,22 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>11169</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="2">
         <v>9127418313</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="3">
         <v>9121413052</v>
       </c>
       <c r="G7" s="1">
@@ -595,124 +613,142 @@
       <c r="A8" s="1">
         <v>111159</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="2">
         <v>9195698562</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>9915921621</v>
       </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="A9" s="4">
         <v>111160</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="5">
         <v>9104723915</v>
       </c>
       <c r="F9" s="6">
         <v>9192793212</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
